--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.62.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.62.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.62.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.62.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.62.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.62.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0062.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0062.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: å�³</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+5373 CJK UNIFIED IDEOGRAPH-5373 | isolated marker/symbol line :: 即</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: vocÃ¨ at the hearing. affidavit.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]55</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]55</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L22: isolated marker/symbol line :: 55</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]55</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,12 +670,12 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: For what exhibits may be so proved, see Danielâ€™s</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206 | isolated marker/symbol line :: 分</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -681,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: &amp;</t>
+          <t>L80: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -723,12 +727,12 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L71: symbol-only separator/garbage line :: 120.</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+5373 CJK UNIFIED IDEOGRAPH-5373 | isolated marker/symbol line :: 即</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: /</t>
+          <t>L82: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -750,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -770,12 +774,12 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 9</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206 | isolated marker/symbol line :: 分</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: -</t>
+          <t>L84: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -817,10 +821,14 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr"/>
+          <t>L71: symbol-only separator/garbage line :: 120.</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L111: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -858,7 +866,11 @@
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L79: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr"/>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
@@ -897,7 +909,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L80: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
@@ -957,12 +973,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1001,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1035,12 +1051,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
